--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2646" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="498">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -737,6 +737,13 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="urn:oid:1.3.6.1.4.1.19376.1.9.2.2"/&gt;
+  &lt;code value="MTPItem"/&gt;
+  &lt;display value="Ligne dans un plan de traitement"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -746,767 +753,641 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>CarePlan.category.coding.id</t>
-  </si>
-  <si>
-    <t>CarePlan.category.coding.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>urn:1.3.6.1.4.1.19376.1.9.2.2</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>CarePlan.category.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>CarePlan.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>IHEPharmacyItemTypeList</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>CarePlan.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Ligne dans un plan de traitement</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CarePlan.category.coding.userSelected</t>
+    <t>CarePlan.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>CarePlan.title</t>
+  </si>
+  <si>
+    <t>Human-friendly name for the care plan</t>
+  </si>
+  <si>
+    <t>Human-friendly name for the care plan.</t>
+  </si>
+  <si>
+    <t>CarePlan.description</t>
+  </si>
+  <si>
+    <t>Summary of nature of plan</t>
+  </si>
+  <si>
+    <t>A description of the scope and nature of the plan.</t>
+  </si>
+  <si>
+    <t>Provides more detail than conveyed by category.</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>CarePlan.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patient
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who the care plan is for</t>
+  </si>
+  <si>
+    <t>Identifies the patient or group whose intended care is described by the plan.</t>
+  </si>
+  <si>
+    <t>Request.subject</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PAT].role[classCode=PAT]</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>PID-3</t>
+  </si>
+  <si>
+    <t>CarePlan.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Encounter created as part of</t>
+  </si>
+  <si>
+    <t>The Encounter during which this CarePlan was created or to which the creation of this record is tightly associated.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. CarePlan activities conducted as a result of the care plan may well occur as part of other encounters.</t>
+  </si>
+  <si>
+    <t>Request.context</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>Associated PV1</t>
+  </si>
+  <si>
+    <t>CarePlan.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timing
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period plan covers</t>
+  </si>
+  <si>
+    <t>Indicates when the plan did (or is intended to) come into effect and end.</t>
+  </si>
+  <si>
+    <t>Any activities scheduled as part of the plan should be constrained to the specified period regardless of whether the activities are planned within a single encounter/episode or across multiple encounters/episodes (e.g. the longitudinal management of a chronic condition).</t>
+  </si>
+  <si>
+    <t>Allows tracking what plan(s) are in effect at a particular time.</t>
+  </si>
+  <si>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.planned</t>
+  </si>
+  <si>
+    <t>GOL-7 / GOL-8</t>
+  </si>
+  <si>
+    <t>CarePlan.created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">authoredOn
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date record was first recorded</t>
+  </si>
+  <si>
+    <t>Represents when this particular CarePlan record was created in the system, which is often a system-generated date.</t>
+  </si>
+  <si>
+    <t>Request.authoredOn</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>CarePlan.author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who is the designated responsible party</t>
+  </si>
+  <si>
+    <t>When populated, the author is responsible for the care plan.  The care plan is attributed to the author.</t>
+  </si>
+  <si>
+    <t>The author may also be a contributor.  For example, an organization can be an author, but not listed as a contributor.</t>
+  </si>
+  <si>
+    <t>Request.requester</t>
+  </si>
+  <si>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>CarePlan.contributor</t>
+  </si>
+  <si>
+    <t>Who provided the content of the care plan</t>
+  </si>
+  <si>
+    <t>Identifies the individual(s) or organization who provided the contents of the care plan.</t>
+  </si>
+  <si>
+    <t>Collaborative care plans may have multiple contributors.</t>
+  </si>
+  <si>
+    <t>CarePlan.careTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CareTeam|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who's involved in plan?</t>
+  </si>
+  <si>
+    <t>Identifies all people and organizations who are expected to be involved in the care envisioned by this plan.</t>
+  </si>
+  <si>
+    <t>Allows representation of care teams, helps scope care plan.  In some cases may be a determiner of access permissions.</t>
+  </si>
+  <si>
+    <t>Request.performer {similar but does not entail CareTeam}</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>CarePlan.addresses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Health issues this plan addresses</t>
+  </si>
+  <si>
+    <t>Identifies the conditions/problems/concerns/diagnoses/etc. whose management and/or mitigation are handled by this plan.</t>
+  </si>
+  <si>
+    <t>When the diagnosis is related to an allergy or intolerance, the Condition and AllergyIntolerance resources can both be used. However, to be actionable for decision support, using Condition alone is not sufficient as the allergy or intolerance condition needs to be represented as an AllergyIntolerance.</t>
+  </si>
+  <si>
+    <t>Links plan to the conditions it manages.  The element can identify risks addressed by the plan as well as active conditions.  (The Condition resource can include things like "at risk for hypertension" or "fall risk".)  Also scopes plans - multiple plans may exist addressing different concerns.</t>
+  </si>
+  <si>
+    <t>Request.reasonReference</t>
+  </si>
+  <si>
+    <t>.actRelationship[typeCode=SUBJ].target[classCode=CONC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>PRB-4</t>
+  </si>
+  <si>
+    <t>CarePlan.supportingInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Information considered as part of plan</t>
+  </si>
+  <si>
+    <t>Identifies portions of the patient's record that specifically influenced the formation of the plan.  These might include comorbidities, recent procedures, limitations, recent assessments, etc.</t>
+  </si>
+  <si>
+    <t>Use "concern" to identify specific conditions addressed by the care plan.</t>
+  </si>
+  <si>
+    <t>Identifies barriers and other considerations associated with the care plan.</t>
+  </si>
+  <si>
+    <t>Request.supportingInfo</t>
+  </si>
+  <si>
+    <t>CarePlan.goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Goal|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Desired outcome of plan</t>
+  </si>
+  <si>
+    <t>Describes the intended objective(s) of carrying out the care plan.</t>
+  </si>
+  <si>
+    <t>Goal can be achieving a particular change or merely maintaining a current state or even slowing a decline.</t>
+  </si>
+  <si>
+    <t>Provides context for plan.  Allows plan effectiveness to be evaluated by clinicians.</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode&lt;=OBJ].</t>
+  </si>
+  <si>
+    <t>GOL.1</t>
+  </si>
+  <si>
+    <t>CarePlan.activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Action to occur as part of plan</t>
+  </si>
+  <si>
+    <t>Identifies a planned action to occur as part of the plan.  For example, a medication to be used, lab tests to perform, self-monitoring, education, etc.</t>
+  </si>
+  <si>
+    <t>Allows systems to prompt for performance of planned activities, and validate plans against best practice.</t>
+  </si>
+  <si>
+    <t>cpl-3:Provide a reference or detail, not both {detail.empty() or reference.empty()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>{no mapping
+NOTE: This is a list of contained Request-Event tuples!}</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].target</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.id</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.outcomeCodeableConcept</t>
+  </si>
+  <si>
+    <t>Results of the activity</t>
+  </si>
+  <si>
+    <t>Identifies the outcome at the point when the status of the activity is assessed.  For example, the outcome of an education activity could be patient understands (or not).</t>
+  </si>
+  <si>
+    <t>Note that this should not duplicate the activity status (e.g. completed or in progress).</t>
+  </si>
+  <si>
+    <t>Identifies the results of the activity.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.outcomeReference</t>
+  </si>
+  <si>
+    <t>Appointment, Encounter, Procedure, etc.</t>
+  </si>
+  <si>
+    <t>Details of the outcome or action resulting from the activity.  The reference to an "event" resource, such as Procedure or Encounter or Observation, is the result/outcome of the activity itself.  The activity can be conveyed using CarePlan.activity.detail OR using the CarePlan.activity.reference (a reference to a “request” resource).</t>
+  </si>
+  <si>
+    <t>The activity outcome is independent of the outcome of the related goal(s).  For example, if the goal is to achieve a target body weight of 150 lbs and an activity is defined to diet, then the activity outcome could be calories consumed whereas the goal outcome is an observation for the actual body weight measured.</t>
+  </si>
+  <si>
+    <t>Links plan to resulting actions.</t>
+  </si>
+  <si>
+    <t>{Event that is outcome of Request in activity.reference}</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=FLFS].source</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Comments about the activity status/progress</t>
+  </si>
+  <si>
+    <t>Notes about the adherence/status/progress of the activity.</t>
+  </si>
+  <si>
+    <t>This element should NOT be used to describe the activity to be performed - that occurs either within the resource pointed to by activity.detail.reference or in activity.detail.description.</t>
+  </si>
+  <si>
+    <t>Can be used to capture information about adherence, progress, concerns, etc.</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="annotation"].value</t>
+  </si>
+  <si>
+    <t>NTE?</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-request-document)
+</t>
+  </si>
+  <si>
+    <t>Activity details defined in specific resource</t>
+  </si>
+  <si>
+    <t>The details of the proposed activity represented in a specific resource.</t>
+  </si>
+  <si>
+    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  +The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
+  </si>
+  <si>
+    <t>Details in a form consistent with other applications and contexts of use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpl-3
+</t>
+  </si>
+  <si>
+    <t>{Request that resulted in Event in activity.actionResulting}</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail</t>
+  </si>
+  <si>
+    <t>In-line definition of activity</t>
+  </si>
+  <si>
+    <t>A simple summary of a planned activity suitable for a general care plan system (e.g. form driven) that doesn't know about specific resources such as procedure etc.</t>
+  </si>
+  <si>
+    <t>Details in a simple form for generic care plan systems.</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.id</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.modifierExtension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.kind</t>
+  </si>
+  <si>
+    <t>Appointment | CommunicationRequest | DeviceRequest | MedicationRequest | NutritionOrder | Task | ServiceRequest | VisionPrescription</t>
+  </si>
+  <si>
+    <t>A description of the kind of resource the in-line definition of a care plan activity is representing.  The CarePlan.activity.detail is an in-line definition when a resource is not referenced using CarePlan.activity.reference.  For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest.</t>
+  </si>
+  <si>
+    <t>May determine what types of extensions are permitted.</t>
+  </si>
+  <si>
+    <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.0.1</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[classCode=LIST].code</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
+  </si>
+  <si>
+    <t>Allows Questionnaires that the patient (or practitioner) should fill in to fulfill the care plan activity.</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.instantiatesUri</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.code</t>
+  </si>
+  <si>
+    <t>Detail type of activity</t>
+  </si>
+  <si>
+    <t>Detailed description of the type of planned activity; e.g. what lab test, what procedure, what kind of encounter.</t>
+  </si>
+  <si>
+    <t>Tends to be less relevant for activities involving particular products.  Codes should not convey negation - use "prohibited" instead.</t>
+  </si>
+  <si>
+    <t>Allows matching performed to planned as well as validation against protocols.</t>
+  </si>
+  <si>
+    <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.code</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>OBR-4 / RXE-2 / RXO-1 / RXD-2</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.reasonCode</t>
+  </si>
+  <si>
+    <t>Why activity should be done or why activity was prohibited</t>
+  </si>
+  <si>
+    <t>Provides the rationale that drove the inclusion of this particular activity as part of the plan or the reason why the activity was prohibited.</t>
+  </si>
+  <si>
+    <t>This could be a diagnosis code.  If a full condition record exists or additional detail is needed, use reasonCondition instead.</t>
+  </si>
+  <si>
+    <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.reasonCode</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.reasonReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Why activity is needed</t>
+  </si>
+  <si>
+    <t>Indicates another resource, such as the health condition(s), whose existence justifies this request and drove the inclusion of this particular activity as part of the plan.</t>
+  </si>
+  <si>
+    <t>Conditions can be identified at the activity level that are not identified as reasons for the overall plan.</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.goal</t>
+  </si>
+  <si>
+    <t>Goals this activity relates to</t>
+  </si>
+  <si>
+    <t>Internal reference that identifies the goals that this activity is intended to contribute towards meeting.</t>
+  </si>
+  <si>
+    <t>So that participants know the link explicitly.</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.status</t>
+  </si>
+  <si>
+    <t>not-started | scheduled | in-progress | on-hold | completed | cancelled | stopped | unknown | entered-in-error</t>
+  </si>
+  <si>
+    <t>Identifies what progress is being made for the specific activity.</t>
+  </si>
+  <si>
+    <t>Some aspects of status can be inferred based on the resources linked in actionTaken.  Note that "status" is only as current as the plan was most recently updated.  
+The unknown code is not to be used to convey other statuses.  The unknown code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the activity.</t>
+  </si>
+  <si>
+    <t>Indicates progress against the plan, whether the activity is still relevant for the plan.</t>
+  </si>
+  <si>
+    <t>Codes that reflect the current state of a care plan activity within its overall life cycle.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.status</t>
+  </si>
+  <si>
+    <t>.statusCode not-started = new scheduled = not-started (and fulfillment relationship to appointent) in-progress = active on-hold = suspended completed = completed cancelled = aborted</t>
+  </si>
+  <si>
+    <t>ORC-5?</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.statusReason</t>
+  </si>
+  <si>
+    <t>Reason for current status</t>
+  </si>
+  <si>
+    <t>Provides reason why the activity isn't yet started, is on hold, was cancelled, etc.</t>
+  </si>
+  <si>
+    <t>Will generally not be present if status is "complete".  Be sure to prompt to update this (or at least remove the existing value) if the status is changed.</t>
+  </si>
+  <si>
+    <t>Request.statusReason</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.doNotPerform</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CarePlan.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>CarePlan.title</t>
-  </si>
-  <si>
-    <t>Human-friendly name for the care plan</t>
-  </si>
-  <si>
-    <t>Human-friendly name for the care plan.</t>
-  </si>
-  <si>
-    <t>CarePlan.description</t>
-  </si>
-  <si>
-    <t>Summary of nature of plan</t>
-  </si>
-  <si>
-    <t>A description of the scope and nature of the plan.</t>
-  </si>
-  <si>
-    <t>Provides more detail than conveyed by category.</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>CarePlan.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patient
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who the care plan is for</t>
-  </si>
-  <si>
-    <t>Identifies the patient or group whose intended care is described by the plan.</t>
-  </si>
-  <si>
-    <t>Request.subject</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PAT].role[classCode=PAT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>PID-3</t>
-  </si>
-  <si>
-    <t>CarePlan.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Encounter created as part of</t>
-  </si>
-  <si>
-    <t>The Encounter during which this CarePlan was created or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. CarePlan activities conducted as a result of the care plan may well occur as part of other encounters.</t>
-  </si>
-  <si>
-    <t>Request.context</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Associated PV1</t>
-  </si>
-  <si>
-    <t>CarePlan.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">timing
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period plan covers</t>
-  </si>
-  <si>
-    <t>Indicates when the plan did (or is intended to) come into effect and end.</t>
-  </si>
-  <si>
-    <t>Any activities scheduled as part of the plan should be constrained to the specified period regardless of whether the activities are planned within a single encounter/episode or across multiple encounters/episodes (e.g. the longitudinal management of a chronic condition).</t>
-  </si>
-  <si>
-    <t>Allows tracking what plan(s) are in effect at a particular time.</t>
-  </si>
-  <si>
-    <t>Request.occurrence[x]</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.planned</t>
-  </si>
-  <si>
-    <t>GOL-7 / GOL-8</t>
-  </si>
-  <si>
-    <t>CarePlan.created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">authoredOn
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date record was first recorded</t>
-  </si>
-  <si>
-    <t>Represents when this particular CarePlan record was created in the system, which is often a system-generated date.</t>
-  </si>
-  <si>
-    <t>Request.authoredOn</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>CarePlan.author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who is the designated responsible party</t>
-  </si>
-  <si>
-    <t>When populated, the author is responsible for the care plan.  The care plan is attributed to the author.</t>
-  </si>
-  <si>
-    <t>The author may also be a contributor.  For example, an organization can be an author, but not listed as a contributor.</t>
-  </si>
-  <si>
-    <t>Request.requester</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>CarePlan.contributor</t>
-  </si>
-  <si>
-    <t>Who provided the content of the care plan</t>
-  </si>
-  <si>
-    <t>Identifies the individual(s) or organization who provided the contents of the care plan.</t>
-  </si>
-  <si>
-    <t>Collaborative care plans may have multiple contributors.</t>
-  </si>
-  <si>
-    <t>CarePlan.careTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CareTeam|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who's involved in plan?</t>
-  </si>
-  <si>
-    <t>Identifies all people and organizations who are expected to be involved in the care envisioned by this plan.</t>
-  </si>
-  <si>
-    <t>Allows representation of care teams, helps scope care plan.  In some cases may be a determiner of access permissions.</t>
-  </si>
-  <si>
-    <t>Request.performer {similar but does not entail CareTeam}</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>CarePlan.addresses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Health issues this plan addresses</t>
-  </si>
-  <si>
-    <t>Identifies the conditions/problems/concerns/diagnoses/etc. whose management and/or mitigation are handled by this plan.</t>
-  </si>
-  <si>
-    <t>When the diagnosis is related to an allergy or intolerance, the Condition and AllergyIntolerance resources can both be used. However, to be actionable for decision support, using Condition alone is not sufficient as the allergy or intolerance condition needs to be represented as an AllergyIntolerance.</t>
-  </si>
-  <si>
-    <t>Links plan to the conditions it manages.  The element can identify risks addressed by the plan as well as active conditions.  (The Condition resource can include things like "at risk for hypertension" or "fall risk".)  Also scopes plans - multiple plans may exist addressing different concerns.</t>
-  </si>
-  <si>
-    <t>Request.reasonReference</t>
-  </si>
-  <si>
-    <t>.actRelationship[typeCode=SUBJ].target[classCode=CONC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>PRB-4</t>
-  </si>
-  <si>
-    <t>CarePlan.supportingInfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Information considered as part of plan</t>
-  </si>
-  <si>
-    <t>Identifies portions of the patient's record that specifically influenced the formation of the plan.  These might include comorbidities, recent procedures, limitations, recent assessments, etc.</t>
-  </si>
-  <si>
-    <t>Use "concern" to identify specific conditions addressed by the care plan.</t>
-  </si>
-  <si>
-    <t>Identifies barriers and other considerations associated with the care plan.</t>
-  </si>
-  <si>
-    <t>Request.supportingInfo</t>
-  </si>
-  <si>
-    <t>CarePlan.goal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Goal|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Desired outcome of plan</t>
-  </si>
-  <si>
-    <t>Describes the intended objective(s) of carrying out the care plan.</t>
-  </si>
-  <si>
-    <t>Goal can be achieving a particular change or merely maintaining a current state or even slowing a decline.</t>
-  </si>
-  <si>
-    <t>Provides context for plan.  Allows plan effectiveness to be evaluated by clinicians.</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode&lt;=OBJ].</t>
-  </si>
-  <si>
-    <t>GOL.1</t>
-  </si>
-  <si>
-    <t>CarePlan.activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Action to occur as part of plan</t>
-  </si>
-  <si>
-    <t>Identifies a planned action to occur as part of the plan.  For example, a medication to be used, lab tests to perform, self-monitoring, education, etc.</t>
-  </si>
-  <si>
-    <t>Allows systems to prompt for performance of planned activities, and validate plans against best practice.</t>
-  </si>
-  <si>
-    <t>cpl-3:Provide a reference or detail, not both {detail.empty() or reference.empty()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>{no mapping
-NOTE: This is a list of contained Request-Event tuples!}</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].target</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.id</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.outcomeCodeableConcept</t>
-  </si>
-  <si>
-    <t>Results of the activity</t>
-  </si>
-  <si>
-    <t>Identifies the outcome at the point when the status of the activity is assessed.  For example, the outcome of an education activity could be patient understands (or not).</t>
-  </si>
-  <si>
-    <t>Note that this should not duplicate the activity status (e.g. completed or in progress).</t>
-  </si>
-  <si>
-    <t>Identifies the results of the activity.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.outcomeReference</t>
-  </si>
-  <si>
-    <t>Appointment, Encounter, Procedure, etc.</t>
-  </si>
-  <si>
-    <t>Details of the outcome or action resulting from the activity.  The reference to an "event" resource, such as Procedure or Encounter or Observation, is the result/outcome of the activity itself.  The activity can be conveyed using CarePlan.activity.detail OR using the CarePlan.activity.reference (a reference to a “request” resource).</t>
-  </si>
-  <si>
-    <t>The activity outcome is independent of the outcome of the related goal(s).  For example, if the goal is to achieve a target body weight of 150 lbs and an activity is defined to diet, then the activity outcome could be calories consumed whereas the goal outcome is an observation for the actual body weight measured.</t>
-  </si>
-  <si>
-    <t>Links plan to resulting actions.</t>
-  </si>
-  <si>
-    <t>{Event that is outcome of Request in activity.reference}</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=FLFS].source</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>Comments about the activity status/progress</t>
-  </si>
-  <si>
-    <t>Notes about the adherence/status/progress of the activity.</t>
-  </si>
-  <si>
-    <t>This element should NOT be used to describe the activity to be performed - that occurs either within the resource pointed to by activity.detail.reference or in activity.detail.description.</t>
-  </si>
-  <si>
-    <t>Can be used to capture information about adherence, progress, concerns, etc.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="annotation"].value</t>
-  </si>
-  <si>
-    <t>NTE?</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-request-document)
-</t>
-  </si>
-  <si>
-    <t>Activity details defined in specific resource</t>
-  </si>
-  <si>
-    <t>The details of the proposed activity represented in a specific resource.</t>
-  </si>
-  <si>
-    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  -The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
-  </si>
-  <si>
-    <t>Details in a form consistent with other applications and contexts of use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpl-3
-</t>
-  </si>
-  <si>
-    <t>{Request that resulted in Event in activity.actionResulting}</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail</t>
-  </si>
-  <si>
-    <t>In-line definition of activity</t>
-  </si>
-  <si>
-    <t>A simple summary of a planned activity suitable for a general care plan system (e.g. form driven) that doesn't know about specific resources such as procedure etc.</t>
-  </si>
-  <si>
-    <t>Details in a simple form for generic care plan systems.</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.id</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.modifierExtension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.kind</t>
-  </si>
-  <si>
-    <t>Appointment | CommunicationRequest | DeviceRequest | MedicationRequest | NutritionOrder | Task | ServiceRequest | VisionPrescription</t>
-  </si>
-  <si>
-    <t>A description of the kind of resource the in-line definition of a care plan activity is representing.  The CarePlan.activity.detail is an in-line definition when a resource is not referenced using CarePlan.activity.reference.  For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest.</t>
-  </si>
-  <si>
-    <t>May determine what types of extensions are permitted.</t>
-  </si>
-  <si>
-    <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.0.1</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=LIST].code</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
-  </si>
-  <si>
-    <t>Allows Questionnaires that the patient (or practitioner) should fill in to fulfill the care plan activity.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.instantiatesUri</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.code</t>
-  </si>
-  <si>
-    <t>Detail type of activity</t>
-  </si>
-  <si>
-    <t>Detailed description of the type of planned activity; e.g. what lab test, what procedure, what kind of encounter.</t>
-  </si>
-  <si>
-    <t>Tends to be less relevant for activities involving particular products.  Codes should not convey negation - use "prohibited" instead.</t>
-  </si>
-  <si>
-    <t>Allows matching performed to planned as well as validation against protocols.</t>
-  </si>
-  <si>
-    <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.code</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>OBR-4 / RXE-2 / RXO-1 / RXD-2</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.reasonCode</t>
-  </si>
-  <si>
-    <t>Why activity should be done or why activity was prohibited</t>
-  </si>
-  <si>
-    <t>Provides the rationale that drove the inclusion of this particular activity as part of the plan or the reason why the activity was prohibited.</t>
-  </si>
-  <si>
-    <t>This could be a diagnosis code.  If a full condition record exists or additional detail is needed, use reasonCondition instead.</t>
-  </si>
-  <si>
-    <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.reasonCode</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Why activity is needed</t>
-  </si>
-  <si>
-    <t>Indicates another resource, such as the health condition(s), whose existence justifies this request and drove the inclusion of this particular activity as part of the plan.</t>
-  </si>
-  <si>
-    <t>Conditions can be identified at the activity level that are not identified as reasons for the overall plan.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.goal</t>
-  </si>
-  <si>
-    <t>Goals this activity relates to</t>
-  </si>
-  <si>
-    <t>Internal reference that identifies the goals that this activity is intended to contribute towards meeting.</t>
-  </si>
-  <si>
-    <t>So that participants know the link explicitly.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.status</t>
-  </si>
-  <si>
-    <t>not-started | scheduled | in-progress | on-hold | completed | cancelled | stopped | unknown | entered-in-error</t>
-  </si>
-  <si>
-    <t>Identifies what progress is being made for the specific activity.</t>
-  </si>
-  <si>
-    <t>Some aspects of status can be inferred based on the resources linked in actionTaken.  Note that "status" is only as current as the plan was most recently updated.  
-The unknown code is not to be used to convey other statuses.  The unknown code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the activity.</t>
-  </si>
-  <si>
-    <t>Indicates progress against the plan, whether the activity is still relevant for the plan.</t>
-  </si>
-  <si>
-    <t>Codes that reflect the current state of a care plan activity within its overall life cycle.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.status</t>
-  </si>
-  <si>
-    <t>.statusCode not-started = new scheduled = not-started (and fulfillment relationship to appointent) in-progress = active on-hold = suspended completed = completed cancelled = aborted</t>
-  </si>
-  <si>
-    <t>ORC-5?</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.statusReason</t>
-  </si>
-  <si>
-    <t>Reason for current status</t>
-  </si>
-  <si>
-    <t>Provides reason why the activity isn't yet started, is on hold, was cancelled, etc.</t>
-  </si>
-  <si>
-    <t>Will generally not be present if status is "complete".  Be sure to prompt to update this (or at least remove the existing value) if the status is changed.</t>
-  </si>
-  <si>
-    <t>Request.statusReason</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.doNotPerform</t>
   </si>
   <si>
     <t>If true, activity is prohibiting action</t>
@@ -2006,7 +1887,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN72"/>
+  <dimension ref="A1:AN65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.58203125" customWidth="true" bestFit="true"/>
@@ -4506,7 +4387,7 @@
         <v>80</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>80</v>
@@ -4545,7 +4426,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4563,21 +4444,21 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4597,19 +4478,23 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4657,7 +4542,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4669,38 +4554,38 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>80</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4709,20 +4594,18 @@
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4759,37 +4642,37 @@
         <v>80</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>221</v>
+        <v>80</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>222</v>
+        <v>80</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>80</v>
@@ -4800,10 +4683,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4826,19 +4709,17 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4848,7 +4729,7 @@
         <v>80</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>80</v>
@@ -4887,7 +4768,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4905,29 +4786,29 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>
@@ -4942,17 +4823,15 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5001,10 +4880,10 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>88</v>
@@ -5016,24 +4895,24 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5056,18 +4935,18 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -5076,7 +4955,7 @@
         <v>80</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>80</v>
@@ -5115,7 +4994,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5130,28 +5009,28 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5170,17 +5049,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5190,7 +5071,7 @@
         <v>80</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>80</v>
@@ -5229,7 +5110,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5244,28 +5125,28 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>80</v>
+        <v>278</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>80</v>
+        <v>281</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5284,20 +5165,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -5345,7 +5222,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5360,24 +5237,24 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>80</v>
+        <v>287</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>276</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5391,7 +5268,7 @@
         <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>80</v>
@@ -5400,20 +5277,18 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>214</v>
+        <v>289</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5461,7 +5336,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5476,24 +5351,24 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>80</v>
+        <v>294</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>284</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5504,7 +5379,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -5513,18 +5388,20 @@
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>214</v>
+        <v>289</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5573,13 +5450,13 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
@@ -5602,10 +5479,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5616,7 +5493,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>80</v>
@@ -5625,20 +5502,20 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>214</v>
+        <v>300</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5687,13 +5564,13 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>80</v>
@@ -5702,13 +5579,13 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5716,21 +5593,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
@@ -5742,16 +5619,20 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
@@ -5799,13 +5680,13 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
@@ -5814,24 +5695,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5842,7 +5723,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5851,21 +5732,23 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
@@ -5913,13 +5796,13 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
@@ -5928,35 +5811,35 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>308</v>
+        <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>309</v>
+        <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>310</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
@@ -5965,22 +5848,22 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6029,13 +5912,13 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
@@ -6044,35 +5927,35 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>323</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -6081,19 +5964,21 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6141,39 +6026,39 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>336</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6187,26 +6072,24 @@
         <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>331</v>
+        <v>214</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6255,7 +6138,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>330</v>
+        <v>217</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6267,16 +6150,16 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>336</v>
+        <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -6284,14 +6167,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6310,16 +6193,16 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>331</v>
+        <v>134</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>135</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>220</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>340</v>
+        <v>137</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6369,7 +6252,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>224</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6381,13 +6264,13 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
@@ -6405,7 +6288,7 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6418,13 +6301,13 @@
         <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>343</v>
@@ -6432,9 +6315,11 @@
       <c r="M39" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N39" s="2"/>
+      <c r="N39" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>345</v>
+        <v>143</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6483,7 +6368,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6495,16 +6380,16 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6512,10 +6397,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6535,23 +6420,21 @@
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>353</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6575,13 +6458,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6599,7 +6482,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6614,24 +6497,24 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>354</v>
+        <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>355</v>
+        <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>357</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6654,19 +6537,19 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>359</v>
+        <v>317</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6715,7 +6598,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6730,10 +6613,10 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
@@ -6744,10 +6627,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6770,19 +6653,19 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -6831,7 +6714,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6849,21 +6732,21 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6874,10 +6757,10 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>80</v>
@@ -6886,17 +6769,19 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -6945,25 +6830,25 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI43" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AJ43" t="s" s="2">
-        <v>378</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>380</v>
+        <v>338</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -6974,10 +6859,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7000,16 +6885,18 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>214</v>
+        <v>332</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>215</v>
+        <v>376</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>216</v>
+        <v>377</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7057,7 +6944,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>217</v>
+        <v>375</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7066,16 +6953,16 @@
         <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>218</v>
+        <v>379</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -7086,21 +6973,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7112,17 +6999,15 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7171,19 +7056,19 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7200,14 +7085,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>384</v>
+        <v>133</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7220,26 +7105,24 @@
         <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>385</v>
+        <v>135</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>386</v>
+        <v>220</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7287,7 +7170,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>387</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7305,7 +7188,7 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7316,14 +7199,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7336,24 +7219,26 @@
         <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>204</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>389</v>
+        <v>343</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>390</v>
+        <v>344</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7377,13 +7262,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>392</v>
+        <v>80</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>393</v>
+        <v>80</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7401,7 +7286,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>388</v>
+        <v>345</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7413,13 +7298,13 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7430,10 +7315,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7444,7 +7329,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7456,19 +7341,17 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>359</v>
+        <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7493,13 +7376,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>80</v>
+        <v>387</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>80</v>
+        <v>388</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7517,13 +7400,13 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
@@ -7532,10 +7415,10 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>399</v>
+        <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
@@ -7546,10 +7429,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7572,19 +7455,17 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>403</v>
+        <v>157</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7633,7 +7514,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7648,24 +7529,24 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>407</v>
+        <v>160</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7676,10 +7557,10 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>80</v>
@@ -7688,19 +7569,19 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>410</v>
+        <v>102</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>411</v>
+        <v>162</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>413</v>
+        <v>164</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7749,25 +7630,25 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>416</v>
+        <v>165</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
@@ -7778,10 +7659,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7804,17 +7685,19 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>374</v>
+        <v>204</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7839,13 +7722,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>80</v>
+        <v>401</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -7863,7 +7746,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7872,30 +7755,30 @@
         <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>80</v>
+        <v>403</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>80</v>
+        <v>405</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7906,7 +7789,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -7918,15 +7801,17 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>215</v>
+        <v>407</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7951,13 +7836,13 @@
         <v>80</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>80</v>
@@ -7975,25 +7860,25 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>217</v>
+        <v>406</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -8004,14 +7889,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8030,16 +7915,16 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>134</v>
+        <v>414</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>135</v>
+        <v>415</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>220</v>
+        <v>416</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>137</v>
+        <v>417</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8089,7 +7974,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>224</v>
+        <v>413</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8101,13 +7986,13 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8118,14 +8003,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>384</v>
+        <v>80</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8138,25 +8023,23 @@
         <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>324</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>143</v>
+        <v>421</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8205,7 +8088,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8217,13 +8100,13 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>131</v>
+        <v>329</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8234,10 +8117,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8245,7 +8128,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
@@ -8254,7 +8137,7 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>80</v>
@@ -8263,14 +8146,16 @@
         <v>108</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8298,10 +8183,10 @@
         <v>189</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8319,10 +8204,10 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>88</v>
@@ -8334,16 +8219,16 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -8362,7 +8247,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
@@ -8374,18 +8259,18 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>435</v>
       </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8439,7 +8324,7 @@
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
@@ -8448,10 +8333,10 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>159</v>
+        <v>436</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
@@ -8462,10 +8347,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8476,86 +8361,88 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>102</v>
+        <v>438</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>162</v>
+        <v>439</v>
       </c>
       <c r="M57" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q57" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="R57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N57" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>436</v>
-      </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
@@ -8564,10 +8451,10 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>165</v>
+        <v>444</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>160</v>
+        <v>445</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
@@ -8578,10 +8465,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8604,19 +8491,17 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>204</v>
+        <v>447</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8641,13 +8526,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>443</v>
+        <v>80</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>444</v>
+        <v>80</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8665,7 +8550,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8680,24 +8565,24 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>445</v>
+        <v>276</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>446</v>
+        <v>277</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8708,7 +8593,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -8720,18 +8605,20 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>204</v>
+        <v>453</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8755,37 +8642,37 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -8794,24 +8681,24 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>454</v>
+        <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8834,18 +8721,20 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8893,7 +8782,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8908,24 +8797,24 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>354</v>
+        <v>465</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>80</v>
+        <v>467</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8936,10 +8825,10 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>80</v>
@@ -8948,18 +8837,16 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>366</v>
+        <v>469</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>463</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -8983,13 +8870,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>80</v>
+        <v>472</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>80</v>
+        <v>473</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9007,13 +8894,13 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
@@ -9025,29 +8912,29 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>371</v>
+        <v>474</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>80</v>
+        <v>475</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>80</v>
+        <v>477</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>88</v>
@@ -9056,25 +8943,23 @@
         <v>80</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>108</v>
+        <v>478</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9099,13 +8984,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>469</v>
+        <v>80</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9123,10 +9008,10 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>88</v>
@@ -9138,24 +9023,24 @@
         <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>471</v>
+        <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9178,17 +9063,15 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>204</v>
+        <v>478</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9237,7 +9120,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9252,24 +9135,24 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>478</v>
+        <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>80</v>
+        <v>487</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>80</v>
+        <v>488</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9286,32 +9169,26 @@
         <v>80</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>269</v>
+        <v>214</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q64" t="s" s="2">
-        <v>484</v>
-      </c>
+      <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9355,7 +9232,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9370,24 +9247,24 @@
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>485</v>
+        <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>80</v>
+        <v>366</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9398,7 +9275,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
@@ -9410,17 +9287,17 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>488</v>
+        <v>360</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9469,13 +9346,13 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
@@ -9484,816 +9361,20 @@
         <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>318</v>
+        <v>497</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>319</v>
+        <v>365</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>408</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN72">
+  <autoFilter ref="A1:AN65">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10303,7 +9384,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI71">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
